--- a/forms/trg/Formulir_TRG_acuetox.xlsx
+++ b/forms/trg/Formulir_TRG_acuetox.xlsx
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="B26" s="7">
-        <f>COUNTA(Anggota!B5:B28)</f>
+        <f>COUNTA(Anggota!B5:B29)</f>
         <v/>
       </c>
     </row>
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="B27" s="7">
-        <f>COUNTA(Anggota!F5:F28)</f>
+        <f>COUNTA(Anggota!F5:F29)</f>
         <v/>
       </c>
     </row>
@@ -832,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -937,20 +937,16 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Dr. drh. Dwi Kesuma Sari, APVet.</t>
+          <t>Dr. Takahiro Ota</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Researcher</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="D5" s="12" t="n"/>
-      <c r="E5" s="11" t="inlineStr">
-        <is>
-          <t>Researcher</t>
-        </is>
-      </c>
+      <c r="E5" s="11" t="n"/>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="12" t="n"/>
@@ -970,7 +966,7 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Prof. Ir. Iqbal Djawad, M.Sc, PhD</t>
+          <t>Dr. drh. Dwi Kesuma Sari, APVet.</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
@@ -1003,7 +999,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Dr. Sri Wahyuni Rahim, ST, M.Si</t>
+          <t>Prof. Ir. Iqbal Djawad, M.Sc, PhD</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
@@ -1036,7 +1032,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Dr. Ir. Shinta Werorilangi, M.Sc</t>
+          <t>Dr. Sri Wahyuni Rahim, ST, M.Si</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
@@ -1069,16 +1065,20 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Yulia Inda Sari Lalombo, S.Pi</t>
+          <t>Dr. Ir. Shinta Werorilangi, M.Sc</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Student</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D9" s="12" t="n"/>
-      <c r="E9" s="11" t="n"/>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>Researcher</t>
+        </is>
+      </c>
       <c r="F9" s="12" t="n"/>
       <c r="G9" s="12" t="n"/>
       <c r="H9" s="12" t="n"/>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Irpan Tasakka, ST, MT</t>
+          <t>Yulia Inda Sari Lalombo, S.Pi</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Nurul Dhafiyah, S.Pi</t>
+          <t>Muhammad Irpan Tasakka, ST, MT</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Sulistiani Mursalin, S.Pi</t>
+          <t>Nurul Dhafiyah, S.Pi</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>drh. Amelia Ramadhani Anshar, M.Si</t>
+          <t>Sulistiani Mursalin, S.Pi</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Ahmad Satari Idris, S. Pi</t>
+          <t>drh. Amelia Ramadhani Anshar, M.Si</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Shafiyah Athifah Syam, S.Pi</t>
+          <t>Ahmad Satari Idris, S. Pi</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Andi Gina Raodatul Jannah, S.Pi</t>
+          <t>Shafiyah Athifah Syam, S.Pi</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
@@ -1281,11 +1281,7 @@
         </is>
       </c>
       <c r="D16" s="12" t="n"/>
-      <c r="E16" s="11" t="inlineStr">
-        <is>
-          <t>AquEtox</t>
-        </is>
-      </c>
+      <c r="E16" s="11" t="n"/>
       <c r="F16" s="12" t="n"/>
       <c r="G16" s="12" t="n"/>
       <c r="H16" s="12" t="n"/>
@@ -1303,10 +1299,22 @@
       <c r="A17" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="12" t="n"/>
-      <c r="C17" s="12" t="n"/>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>Andi Gina Raodatul Jannah, S.Pi</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
       <c r="D17" s="12" t="n"/>
-      <c r="E17" s="11" t="n"/>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>AquEtox</t>
+        </is>
+      </c>
       <c r="F17" s="12" t="n"/>
       <c r="G17" s="12" t="n"/>
       <c r="H17" s="12" t="n"/>
@@ -1314,7 +1322,11 @@
       <c r="J17" s="12" t="n"/>
       <c r="K17" s="12" t="n"/>
       <c r="L17" s="12" t="n"/>
-      <c r="M17" s="12" t="n"/>
+      <c r="M17" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -1503,15 +1515,32 @@
       <c r="L28" s="12" t="n"/>
       <c r="M28" s="12" t="n"/>
     </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="12" t="n"/>
+      <c r="C29" s="12" t="n"/>
+      <c r="D29" s="12" t="n"/>
+      <c r="E29" s="11" t="n"/>
+      <c r="F29" s="12" t="n"/>
+      <c r="G29" s="12" t="n"/>
+      <c r="H29" s="12" t="n"/>
+      <c r="I29" s="12" t="n"/>
+      <c r="J29" s="12" t="n"/>
+      <c r="K29" s="12" t="n"/>
+      <c r="L29" s="12" t="n"/>
+      <c r="M29" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
